--- a/reports/20260507/API_Upload_Empty_Attachment_claude.xlsx
+++ b/reports/20260507/API_Upload_Empty_Attachment_claude.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +33,8 @@
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +49,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -88,9 +79,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -562,7 +550,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>candidateId=1759</t>
+          <t>candidateId=1809</t>
         </is>
       </c>
     </row>
@@ -609,7 +597,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>candidateId=1765</t>
+          <t>candidateId=1815</t>
         </is>
       </c>
     </row>
@@ -1824,14 +1812,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>status=None, is_ssrf_violated=False, xss_reflected=False</t>
+          <t>status=KO, is_ssrf_violated=True, xss_reflected=False</t>
         </is>
       </c>
     </row>
